--- a/src/Excelsior.Tests/ColumnWidths.MaxWidthFluentZeroRows.verified.xlsx
+++ b/src/Excelsior.Tests/ColumnWidths.MaxWidthFluentZeroRows.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -96,4 +96,18 @@
   </sheetData>
   <autoFilter ref="A1:G1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Id"/>
+    <column index="2" property="Name"/>
+    <column index="3" property="Email"/>
+    <column index="4" property="HireDate"/>
+    <column index="5" property="Salary"/>
+    <column index="6" property="IsActive"/>
+    <column index="7" property="Status"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/ColumnWidths.MaxWidthFluentZeroRows.verified.xlsx
+++ b/src/Excelsior.Tests/ColumnWidths.MaxWidthFluentZeroRows.verified.xlsx
@@ -47,11 +47,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
